--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50343-2024 artfynd.xlsx
+++ b/artfynd/A 50343-2024 artfynd.xlsx
@@ -1129,7 +1129,7 @@
         <v>136216371</v>
       </c>
       <c r="B6" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
